--- a/curation/draft/package18/R18_BC_DSS_BrCa_TAUG.xlsx
+++ b/curation/draft/package18/R18_BC_DSS_BrCa_TAUG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3BCA83-3D65-484B-B269-B299B23C8A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D212C5-0B53-449C-B5DF-5690C9990982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9C2B54C0-060B-496F-B408-7D0F2041239C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{9C2B54C0-060B-496F-B408-7D0F2041239C}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_BrCa" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4216" uniqueCount="522">
   <si>
     <t>package_date</t>
   </si>
@@ -1607,6 +1607,9 @@
   </si>
   <si>
     <t>NEW_DEC2</t>
+  </si>
+  <si>
+    <t>QRS;Clinical or Research Assessment Classification;AJCC Cancer Staging Manual</t>
   </si>
 </sst>
 </file>
@@ -4045,7 +4048,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="39" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>58</v>
       </c>
@@ -4061,7 +4064,9 @@
       <c r="E42" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>521</v>
+      </c>
       <c r="G42" s="4" t="s">
         <v>222</v>
       </c>
@@ -14042,9 +14047,7 @@
       </c>
       <c r="AC93" s="4"/>
       <c r="AD93" s="4"/>
-      <c r="AE93" s="4" t="s">
-        <v>169</v>
-      </c>
+      <c r="AE93" s="4"/>
       <c r="AF93" s="4"/>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.25">
@@ -14594,9 +14597,7 @@
       </c>
       <c r="AC100" s="4"/>
       <c r="AD100" s="4"/>
-      <c r="AE100" s="4" t="s">
-        <v>169</v>
-      </c>
+      <c r="AE100" s="4"/>
       <c r="AF100" s="4"/>
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
@@ -15146,9 +15147,7 @@
       </c>
       <c r="AC107" s="4"/>
       <c r="AD107" s="4"/>
-      <c r="AE107" s="4" t="s">
-        <v>169</v>
-      </c>
+      <c r="AE107" s="4"/>
       <c r="AF107" s="4"/>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.25">
@@ -15698,9 +15697,7 @@
       </c>
       <c r="AC114" s="4"/>
       <c r="AD114" s="4"/>
-      <c r="AE114" s="4" t="s">
-        <v>169</v>
-      </c>
+      <c r="AE114" s="4"/>
       <c r="AF114" s="4"/>
     </row>
     <row r="115" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -16250,9 +16247,7 @@
       </c>
       <c r="AC121" s="4"/>
       <c r="AD121" s="4"/>
-      <c r="AE121" s="4" t="s">
-        <v>169</v>
-      </c>
+      <c r="AE121" s="4"/>
       <c r="AF121" s="4"/>
     </row>
     <row r="122" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">

--- a/curation/draft/package18/R18_BC_DSS_BrCa_TAUG.xlsx
+++ b/curation/draft/package18/R18_BC_DSS_BrCa_TAUG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D212C5-0B53-449C-B5DF-5690C9990982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA5AE5B-28DC-4AF0-BEBC-5BAD845CF067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{9C2B54C0-060B-496F-B408-7D0F2041239C}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" xr2:uid="{9C2B54C0-060B-496F-B408-7D0F2041239C}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_BrCa" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BC_BrCa!$A$1:$R$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SDTM_BrCa!$A$1:$AF$138</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4216" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="522">
   <si>
     <t>package_date</t>
   </si>
@@ -1616,7 +1616,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2148,20 +2148,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02DBC567-A798-4813-83E1-012FB631D130}">
-  <dimension ref="A1:R100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R101"/>
+  <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36.7109375" customWidth="1"/>
-    <col min="7" max="7" width="40.5703125" customWidth="1"/>
-    <col min="9" max="9" width="54.5703125" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.7109375" customWidth="1"/>
-    <col min="17" max="17" width="42.28515625" customWidth="1"/>
-    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.29296875" customWidth="1"/>
+    <col min="6" max="6" width="36.703125" customWidth="1"/>
+    <col min="7" max="7" width="40.5859375" customWidth="1"/>
+    <col min="9" max="9" width="54.5859375" customWidth="1"/>
+    <col min="13" max="13" width="11.41015625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.703125" customWidth="1"/>
+    <col min="17" max="17" width="42.29296875" customWidth="1"/>
+    <col min="18" max="18" width="17.703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="3" customFormat="1" ht="14.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="37">
       <c r="A2" s="7" t="s">
         <v>58</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="37">
       <c r="A3" s="7" t="s">
         <v>58</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="37">
       <c r="A4" s="7" t="s">
         <v>58</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="37">
       <c r="A5" s="7" t="s">
         <v>58</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="37">
       <c r="A6" s="7" t="s">
         <v>58</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="37">
       <c r="A7" s="7" t="s">
         <v>58</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="37">
       <c r="A8" s="7" t="s">
         <v>58</v>
       </c>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="37">
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="37">
       <c r="A10" s="7" t="s">
         <v>58</v>
       </c>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="37">
       <c r="A11" s="7" t="s">
         <v>58</v>
       </c>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="Q11" s="5"/>
     </row>
-    <row r="12" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="37">
       <c r="A12" s="7" t="s">
         <v>58</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="37">
       <c r="A13" s="7" t="s">
         <v>58</v>
       </c>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="37">
       <c r="A14" s="7" t="s">
         <v>58</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="37">
       <c r="A15" s="7" t="s">
         <v>58</v>
       </c>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18">
       <c r="A16" s="7" t="s">
         <v>58</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18">
       <c r="A17" s="7" t="s">
         <v>58</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18">
       <c r="A18" s="7" t="s">
         <v>58</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18">
       <c r="A19" s="7" t="s">
         <v>58</v>
       </c>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18">
       <c r="A20" s="7" t="s">
         <v>58</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18">
       <c r="A21" s="7" t="s">
         <v>58</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18">
       <c r="A22" s="7" t="s">
         <v>58</v>
       </c>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Q22" s="5"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18">
       <c r="A23" s="7" t="s">
         <v>58</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18">
       <c r="A24" s="7" t="s">
         <v>58</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18">
       <c r="A25" s="7" t="s">
         <v>58</v>
       </c>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18">
       <c r="A26" s="7" t="s">
         <v>58</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="25">
       <c r="A27" s="7" t="s">
         <v>58</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="25">
       <c r="A28" s="7" t="s">
         <v>58</v>
       </c>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="Q28" s="5"/>
     </row>
-    <row r="29" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="25">
       <c r="A29" s="7" t="s">
         <v>58</v>
       </c>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="Q29" s="5"/>
     </row>
-    <row r="30" spans="1:18" ht="77.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="61">
       <c r="A30" s="7" t="s">
         <v>58</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="25">
       <c r="A31" s="7" t="s">
         <v>58</v>
       </c>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Q31" s="5"/>
     </row>
-    <row r="32" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="25">
       <c r="A32" s="7" t="s">
         <v>58</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="25">
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="25">
       <c r="A34" s="7" t="s">
         <v>58</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="25">
       <c r="A35" s="7" t="s">
         <v>58</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="25">
       <c r="A36" s="7" t="s">
         <v>58</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="25">
       <c r="A37" s="7" t="s">
         <v>58</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="25">
       <c r="A38" s="7" t="s">
         <v>58</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="37">
       <c r="A39" s="7" t="s">
         <v>58</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="25">
       <c r="A40" s="7" t="s">
         <v>58</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="25">
       <c r="A41" s="7" t="s">
         <v>58</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="39" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="25">
       <c r="A42" s="7" t="s">
         <v>58</v>
       </c>
@@ -4083,7 +4083,7 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="5"/>
     </row>
-    <row r="43" spans="1:17" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="49">
       <c r="A43" s="7" t="s">
         <v>58</v>
       </c>
@@ -4118,7 +4118,7 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="25">
       <c r="A44" s="7" t="s">
         <v>58</v>
       </c>
@@ -4151,7 +4151,7 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="5"/>
     </row>
-    <row r="45" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="49">
       <c r="A45" s="7" t="s">
         <v>58</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="49">
       <c r="A46" s="7" t="s">
         <v>58</v>
       </c>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="Q46" s="5"/>
     </row>
-    <row r="47" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="49">
       <c r="A47" s="7" t="s">
         <v>58</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="49">
       <c r="A48" s="7" t="s">
         <v>58</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="49">
       <c r="A49" s="7" t="s">
         <v>58</v>
       </c>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="Q49" s="5"/>
     </row>
-    <row r="50" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="49">
       <c r="A50" s="7" t="s">
         <v>58</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="49">
       <c r="A51" s="7" t="s">
         <v>58</v>
       </c>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Q51" s="5"/>
     </row>
-    <row r="52" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="49">
       <c r="A52" s="7" t="s">
         <v>58</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="49">
       <c r="A53" s="7" t="s">
         <v>58</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="49">
       <c r="A54" s="7" t="s">
         <v>58</v>
       </c>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="Q54" s="5"/>
     </row>
-    <row r="55" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="49">
       <c r="A55" s="7" t="s">
         <v>58</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="49">
       <c r="A56" s="7" t="s">
         <v>58</v>
       </c>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Q56" s="5"/>
     </row>
-    <row r="57" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" ht="49">
       <c r="A57" s="7" t="s">
         <v>58</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" ht="49">
       <c r="A58" s="7" t="s">
         <v>58</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="49">
       <c r="A59" s="7" t="s">
         <v>58</v>
       </c>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="Q59" s="5"/>
     </row>
-    <row r="60" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" ht="49">
       <c r="A60" s="7" t="s">
         <v>58</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" ht="49">
       <c r="A61" s="7" t="s">
         <v>58</v>
       </c>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="Q61" s="5"/>
     </row>
-    <row r="62" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="49">
       <c r="A62" s="7" t="s">
         <v>58</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="49">
       <c r="A63" s="7" t="s">
         <v>58</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="49">
       <c r="A64" s="7" t="s">
         <v>58</v>
       </c>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="Q64" s="5"/>
     </row>
-    <row r="65" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="49">
       <c r="A65" s="7" t="s">
         <v>58</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="49">
       <c r="A66" s="7" t="s">
         <v>58</v>
       </c>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="Q66" s="5"/>
     </row>
-    <row r="67" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="49">
       <c r="A67" s="7" t="s">
         <v>58</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="49">
       <c r="A68" s="7" t="s">
         <v>58</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="49">
       <c r="A69" s="7" t="s">
         <v>58</v>
       </c>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="Q69" s="5"/>
     </row>
-    <row r="70" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="25">
       <c r="A70" s="7" t="s">
         <v>58</v>
       </c>
@@ -5287,7 +5287,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="5"/>
     </row>
-    <row r="71" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="25">
       <c r="A71" s="7" t="s">
         <v>58</v>
       </c>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="Q71" s="5"/>
     </row>
-    <row r="72" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" ht="25">
       <c r="A72" s="7" t="s">
         <v>58</v>
       </c>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="Q72" s="5"/>
     </row>
-    <row r="73" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" ht="25">
       <c r="A73" s="7" t="s">
         <v>58</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="25">
       <c r="A74" s="7" t="s">
         <v>58</v>
       </c>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="Q74" s="5"/>
     </row>
-    <row r="75" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" ht="25">
       <c r="A75" s="7" t="s">
         <v>58</v>
       </c>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="Q75" s="5"/>
     </row>
-    <row r="76" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" ht="25">
       <c r="A76" s="7" t="s">
         <v>58</v>
       </c>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Q76" s="5"/>
     </row>
-    <row r="77" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="25">
       <c r="A77" s="7" t="s">
         <v>58</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" ht="25">
       <c r="A78" s="7" t="s">
         <v>58</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" ht="25">
       <c r="A79" s="7" t="s">
         <v>58</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" ht="25">
       <c r="A80" s="7" t="s">
         <v>58</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" ht="25">
       <c r="A81" s="7" t="s">
         <v>58</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" ht="25">
       <c r="A82" s="7" t="s">
         <v>58</v>
       </c>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="Q82" s="5"/>
     </row>
-    <row r="83" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" ht="25">
       <c r="A83" s="7" t="s">
         <v>58</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" ht="25">
       <c r="A84" s="7" t="s">
         <v>58</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" ht="25">
       <c r="A85" s="7" t="s">
         <v>58</v>
       </c>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="Q85" s="5"/>
     </row>
-    <row r="86" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17">
       <c r="A86" s="7" t="s">
         <v>58</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17">
       <c r="A87" s="7" t="s">
         <v>58</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17">
       <c r="A88" s="7" t="s">
         <v>58</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17">
       <c r="A89" s="7" t="s">
         <v>58</v>
       </c>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="Q89" s="5"/>
     </row>
-    <row r="90" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17">
       <c r="A90" s="7" t="s">
         <v>58</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17">
       <c r="A91" s="7" t="s">
         <v>58</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17">
       <c r="A92" s="7" t="s">
         <v>58</v>
       </c>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="Q92" s="5"/>
     </row>
-    <row r="93" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17">
       <c r="A93" s="7" t="s">
         <v>58</v>
       </c>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="Q93" s="5"/>
     </row>
-    <row r="94" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17">
       <c r="A94" s="7" t="s">
         <v>58</v>
       </c>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Q94" s="5"/>
     </row>
-    <row r="95" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17">
       <c r="A95" s="7" t="s">
         <v>58</v>
       </c>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="Q95" s="5"/>
     </row>
-    <row r="96" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17">
       <c r="A96" s="7" t="s">
         <v>58</v>
       </c>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="Q96" s="5"/>
     </row>
-    <row r="97" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17">
       <c r="A97" s="7" t="s">
         <v>58</v>
       </c>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="Q97" s="5"/>
     </row>
-    <row r="98" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17">
       <c r="A98" s="7" t="s">
         <v>58</v>
       </c>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="Q98" s="5"/>
     </row>
-    <row r="99" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17">
       <c r="A99" s="7" t="s">
         <v>58</v>
       </c>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="Q99" s="5"/>
     </row>
-    <row r="100" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17">
       <c r="A100" s="7" t="s">
         <v>58</v>
       </c>
@@ -6662,6 +6662,53 @@
         <v>26</v>
       </c>
       <c r="Q100" s="5"/>
+    </row>
+    <row r="101" spans="1:17">
+      <c r="A101" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="N101" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="O101" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="P101" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q101" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R100" xr:uid="{02DBC567-A798-4813-83E1-012FB631D130}"/>
@@ -6892,6 +6939,9 @@
     <hyperlink ref="D21" r:id="rId223" xr:uid="{2B8C6133-6134-411A-B661-D781243AEC2F}"/>
     <hyperlink ref="E21" r:id="rId224" xr:uid="{777D069D-078B-4038-A315-97F5CE542B6B}"/>
     <hyperlink ref="N21" r:id="rId225" xr:uid="{4421D651-7E02-4109-9E92-E573BA4237B5}"/>
+    <hyperlink ref="N101" r:id="rId226" xr:uid="{4F63612B-C5AE-4DA8-8615-D1FC08675ABE}"/>
+    <hyperlink ref="D101" r:id="rId227" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C15329" xr:uid="{D63A1BC1-2620-448D-A7E8-79869E1A002F}"/>
+    <hyperlink ref="E101" r:id="rId228" display="https://evsexplore.semantics.cancer.gov/evsexplore/concept/ncit/C25218" xr:uid="{5C0322A3-3CA7-4D4E-8594-E91E25F60641}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6900,25 +6950,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D118C320-5B2C-4B05-837B-4243603672BC}">
   <dimension ref="A1:AF138"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35"/>
   <cols>
     <col min="3" max="4" width="9" style="12"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="8" width="39.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" customWidth="1"/>
-    <col min="15" max="15" width="49.85546875" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" customWidth="1"/>
-    <col min="21" max="21" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.87890625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.29296875" customWidth="1"/>
+    <col min="8" max="8" width="39.29296875" customWidth="1"/>
+    <col min="9" max="9" width="15.41015625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1171875" customWidth="1"/>
+    <col min="13" max="13" width="9.703125" customWidth="1"/>
+    <col min="15" max="15" width="49.87890625" customWidth="1"/>
+    <col min="16" max="16" width="12.703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.41015625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5859375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.29296875" customWidth="1"/>
+    <col min="21" max="21" width="21.29296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.41015625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="37.700000000000003">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -7016,7 +7066,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32">
       <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
@@ -7092,7 +7142,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
     </row>
-    <row r="3" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="25">
       <c r="A3" s="4" t="s">
         <v>58</v>
       </c>
@@ -7168,7 +7218,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
     </row>
-    <row r="4" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" ht="25">
       <c r="A4" s="4" t="s">
         <v>58</v>
       </c>
@@ -7252,7 +7302,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
     </row>
-    <row r="5" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32">
       <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
@@ -7336,7 +7386,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32">
       <c r="A6" s="4" t="s">
         <v>58</v>
       </c>
@@ -7412,7 +7462,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32">
       <c r="A7" s="4" t="s">
         <v>58</v>
       </c>
@@ -7488,7 +7538,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32">
       <c r="A8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7548,7 +7598,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32">
       <c r="A9" s="4" t="s">
         <v>58</v>
       </c>
@@ -7622,7 +7672,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32">
       <c r="A10" s="4" t="s">
         <v>58</v>
       </c>
@@ -7696,7 +7746,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32">
       <c r="A11" s="4" t="s">
         <v>58</v>
       </c>
@@ -7768,7 +7818,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32">
       <c r="A12" s="4" t="s">
         <v>58</v>
       </c>
@@ -7840,7 +7890,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32">
       <c r="A13" s="4" t="s">
         <v>58</v>
       </c>
@@ -7908,7 +7958,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
     </row>
-    <row r="14" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" ht="25">
       <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
@@ -7986,7 +8036,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="25">
       <c r="A15" s="4" t="s">
         <v>58</v>
       </c>
@@ -8064,7 +8114,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
     </row>
-    <row r="16" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="25">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
@@ -8148,7 +8198,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
     </row>
-    <row r="17" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="25">
       <c r="A17" s="4" t="s">
         <v>58</v>
       </c>
@@ -8232,7 +8282,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="25">
       <c r="A18" s="4" t="s">
         <v>58</v>
       </c>
@@ -8308,7 +8358,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
     </row>
-    <row r="19" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" ht="25">
       <c r="A19" s="4" t="s">
         <v>58</v>
       </c>
@@ -8384,7 +8434,7 @@
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
     </row>
-    <row r="20" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="25">
       <c r="A20" s="4" t="s">
         <v>58</v>
       </c>
@@ -8460,7 +8510,7 @@
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" ht="25">
       <c r="A21" s="4" t="s">
         <v>58</v>
       </c>
@@ -8534,7 +8584,7 @@
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
     </row>
-    <row r="22" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" ht="25">
       <c r="A22" s="4" t="s">
         <v>58</v>
       </c>
@@ -8612,7 +8662,7 @@
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" ht="25">
       <c r="A23" s="4" t="s">
         <v>58</v>
       </c>
@@ -8690,7 +8740,7 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="25">
       <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
@@ -8774,7 +8824,7 @@
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
     </row>
-    <row r="25" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="25">
       <c r="A25" s="4" t="s">
         <v>58</v>
       </c>
@@ -8858,7 +8908,7 @@
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
     </row>
-    <row r="26" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="25">
       <c r="A26" s="4" t="s">
         <v>58</v>
       </c>
@@ -8934,7 +8984,7 @@
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
     </row>
-    <row r="27" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="25">
       <c r="A27" s="4" t="s">
         <v>58</v>
       </c>
@@ -9010,7 +9060,7 @@
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
     </row>
-    <row r="28" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="25">
       <c r="A28" s="4" t="s">
         <v>58</v>
       </c>
@@ -9086,7 +9136,7 @@
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
     </row>
-    <row r="29" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" ht="25">
       <c r="A29" s="4" t="s">
         <v>58</v>
       </c>
@@ -9160,7 +9210,7 @@
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32">
       <c r="A30" s="4" t="s">
         <v>58</v>
       </c>
@@ -9240,7 +9290,7 @@
       </c>
       <c r="AF30" s="4"/>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32">
       <c r="A31" s="4" t="s">
         <v>58</v>
       </c>
@@ -9318,7 +9368,7 @@
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32">
       <c r="A32" s="4" t="s">
         <v>58</v>
       </c>
@@ -9398,7 +9448,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32">
       <c r="A33" s="4" t="s">
         <v>58</v>
       </c>
@@ -9478,7 +9528,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32">
       <c r="A34" s="4" t="s">
         <v>58</v>
       </c>
@@ -9560,7 +9610,7 @@
       </c>
       <c r="AF34" s="4"/>
     </row>
-    <row r="35" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" ht="25">
       <c r="A35" s="4" t="s">
         <v>58</v>
       </c>
@@ -9642,7 +9692,7 @@
       </c>
       <c r="AF35" s="4"/>
     </row>
-    <row r="36" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" ht="28.7">
       <c r="A36" s="4" t="s">
         <v>58</v>
       </c>
@@ -9722,7 +9772,7 @@
       </c>
       <c r="AF36" s="13"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32">
       <c r="A37" s="4" t="s">
         <v>58</v>
       </c>
@@ -9790,7 +9840,7 @@
       <c r="AE37" s="13"/>
       <c r="AF37" s="13"/>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32">
       <c r="A38" s="4" t="s">
         <v>58</v>
       </c>
@@ -9854,7 +9904,7 @@
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
     </row>
-    <row r="39" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" ht="25">
       <c r="A39" s="4" t="s">
         <v>58</v>
       </c>
@@ -9932,7 +9982,7 @@
       </c>
       <c r="AF39" s="4"/>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32">
       <c r="A40" s="4" t="s">
         <v>58</v>
       </c>
@@ -10006,7 +10056,7 @@
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
     </row>
-    <row r="41" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" ht="25">
       <c r="A41" s="4" t="s">
         <v>58</v>
       </c>
@@ -10082,7 +10132,7 @@
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32">
       <c r="A42" s="4" t="s">
         <v>58</v>
       </c>
@@ -10158,7 +10208,7 @@
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
     </row>
-    <row r="43" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" ht="25">
       <c r="A43" s="4" t="s">
         <v>58</v>
       </c>
@@ -10234,7 +10284,7 @@
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32">
       <c r="A44" s="4" t="s">
         <v>58</v>
       </c>
@@ -10304,7 +10354,7 @@
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32">
       <c r="A45" s="4" t="s">
         <v>58</v>
       </c>
@@ -10374,7 +10424,7 @@
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
     </row>
-    <row r="46" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" ht="25">
       <c r="A46" s="4" t="s">
         <v>58</v>
       </c>
@@ -10454,7 +10504,7 @@
       <c r="AE46" s="4"/>
       <c r="AF46" s="4"/>
     </row>
-    <row r="47" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32">
       <c r="A47" s="4" t="s">
         <v>58</v>
       </c>
@@ -10534,7 +10584,7 @@
       <c r="AE47" s="4"/>
       <c r="AF47" s="4"/>
     </row>
-    <row r="48" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" ht="25">
       <c r="A48" s="4" t="s">
         <v>58</v>
       </c>
@@ -10608,7 +10658,7 @@
       <c r="AE48" s="4"/>
       <c r="AF48" s="4"/>
     </row>
-    <row r="49" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" ht="25">
       <c r="A49" s="4" t="s">
         <v>58</v>
       </c>
@@ -10682,7 +10732,7 @@
       <c r="AE49" s="4"/>
       <c r="AF49" s="4"/>
     </row>
-    <row r="50" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" ht="25">
       <c r="A50" s="4" t="s">
         <v>58</v>
       </c>
@@ -10758,7 +10808,7 @@
       <c r="AE50" s="4"/>
       <c r="AF50" s="4"/>
     </row>
-    <row r="51" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" ht="25">
       <c r="A51" s="4" t="s">
         <v>58</v>
       </c>
@@ -10834,7 +10884,7 @@
       <c r="AE51" s="4"/>
       <c r="AF51" s="4"/>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32">
       <c r="A52" s="4" t="s">
         <v>58</v>
       </c>
@@ -10914,7 +10964,7 @@
       <c r="AE52" s="4"/>
       <c r="AF52" s="4"/>
     </row>
-    <row r="53" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32">
       <c r="A53" s="4" t="s">
         <v>58</v>
       </c>
@@ -10994,7 +11044,7 @@
       <c r="AE53" s="4"/>
       <c r="AF53" s="4"/>
     </row>
-    <row r="54" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" ht="25">
       <c r="A54" s="4" t="s">
         <v>58</v>
       </c>
@@ -11072,7 +11122,7 @@
       <c r="AE54" s="4"/>
       <c r="AF54" s="4"/>
     </row>
-    <row r="55" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" ht="25">
       <c r="A55" s="4" t="s">
         <v>58</v>
       </c>
@@ -11146,7 +11196,7 @@
       <c r="AE55" s="4"/>
       <c r="AF55" s="4"/>
     </row>
-    <row r="56" spans="1:32" ht="39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" ht="25">
       <c r="A56" s="4" t="s">
         <v>58</v>
       </c>
@@ -11226,7 +11276,7 @@
       <c r="AE56" s="4"/>
       <c r="AF56" s="4"/>
     </row>
-    <row r="57" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" ht="25">
       <c r="A57" s="4" t="s">
         <v>58</v>
       </c>
@@ -11302,7 +11352,7 @@
       <c r="AE57" s="4"/>
       <c r="AF57" s="4"/>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32">
       <c r="A58" s="4" t="s">
         <v>58</v>
       </c>
@@ -11376,7 +11426,7 @@
       <c r="AE58" s="4"/>
       <c r="AF58" s="4"/>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32">
       <c r="A59" s="4" t="s">
         <v>58</v>
       </c>
@@ -11450,7 +11500,7 @@
       <c r="AE59" s="4"/>
       <c r="AF59" s="4"/>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32">
       <c r="A60" s="4" t="s">
         <v>58</v>
       </c>
@@ -11520,7 +11570,7 @@
       <c r="AE60" s="4"/>
       <c r="AF60" s="4"/>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32">
       <c r="A61" s="4" t="s">
         <v>58</v>
       </c>
@@ -11584,7 +11634,7 @@
       <c r="AE61" s="4"/>
       <c r="AF61" s="4"/>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32">
       <c r="A62" s="4" t="s">
         <v>58</v>
       </c>
@@ -11654,7 +11704,7 @@
       <c r="AE62" s="4"/>
       <c r="AF62" s="4"/>
     </row>
-    <row r="63" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" ht="25">
       <c r="A63" s="4" t="s">
         <v>58</v>
       </c>
@@ -11734,7 +11784,7 @@
       <c r="AE63" s="4"/>
       <c r="AF63" s="4"/>
     </row>
-    <row r="64" spans="1:32" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" ht="14.7" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>58</v>
       </c>
@@ -11814,7 +11864,7 @@
       <c r="AE64" s="4"/>
       <c r="AF64" s="4"/>
     </row>
-    <row r="65" spans="1:32" ht="88.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" ht="88.35" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>58</v>
       </c>
@@ -11892,7 +11942,7 @@
       <c r="AE65" s="4"/>
       <c r="AF65" s="4"/>
     </row>
-    <row r="66" spans="1:32" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="14.7" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>58</v>
       </c>
@@ -11974,7 +12024,7 @@
       <c r="AE66" s="4"/>
       <c r="AF66" s="4"/>
     </row>
-    <row r="67" spans="1:32" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="14.7" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>58</v>
       </c>
@@ -12044,7 +12094,7 @@
       <c r="AE67" s="4"/>
       <c r="AF67" s="4"/>
     </row>
-    <row r="68" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="25">
       <c r="A68" s="4" t="s">
         <v>58</v>
       </c>
@@ -12114,7 +12164,7 @@
       <c r="AE68" s="4"/>
       <c r="AF68" s="4"/>
     </row>
-    <row r="69" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" ht="25">
       <c r="A69" s="4" t="s">
         <v>58</v>
       </c>
@@ -12194,7 +12244,7 @@
       <c r="AE69" s="4"/>
       <c r="AF69" s="4"/>
     </row>
-    <row r="70" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32">
       <c r="A70" s="4" t="s">
         <v>58</v>
       </c>
@@ -12274,7 +12324,7 @@
       <c r="AE70" s="4"/>
       <c r="AF70" s="4"/>
     </row>
-    <row r="71" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="25">
       <c r="A71" s="4" t="s">
         <v>58</v>
       </c>
@@ -12350,7 +12400,7 @@
       <c r="AE71" s="4"/>
       <c r="AF71" s="4"/>
     </row>
-    <row r="72" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="25">
       <c r="A72" s="4" t="s">
         <v>58</v>
       </c>
@@ -12426,7 +12476,7 @@
       <c r="AE72" s="4"/>
       <c r="AF72" s="4"/>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32">
       <c r="A73" s="4" t="s">
         <v>58</v>
       </c>
@@ -12504,7 +12554,7 @@
       <c r="AE73" s="4"/>
       <c r="AF73" s="4"/>
     </row>
-    <row r="74" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" ht="25">
       <c r="A74" s="4" t="s">
         <v>58</v>
       </c>
@@ -12584,7 +12634,7 @@
       <c r="AE74" s="4"/>
       <c r="AF74" s="4"/>
     </row>
-    <row r="75" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="25">
       <c r="A75" s="4" t="s">
         <v>58</v>
       </c>
@@ -12666,7 +12716,7 @@
       <c r="AE75" s="4"/>
       <c r="AF75" s="4"/>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32">
       <c r="A76" s="4" t="s">
         <v>58</v>
       </c>
@@ -12740,7 +12790,7 @@
       <c r="AE76" s="4"/>
       <c r="AF76" s="4"/>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32">
       <c r="A77" s="4" t="s">
         <v>58</v>
       </c>
@@ -12814,7 +12864,7 @@
       <c r="AE77" s="4"/>
       <c r="AF77" s="4"/>
     </row>
-    <row r="78" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" ht="25">
       <c r="A78" s="4" t="s">
         <v>58</v>
       </c>
@@ -12896,7 +12946,7 @@
       <c r="AE78" s="4"/>
       <c r="AF78" s="4"/>
     </row>
-    <row r="79" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32">
       <c r="A79" s="4" t="s">
         <v>58</v>
       </c>
@@ -12978,7 +13028,7 @@
       <c r="AE79" s="4"/>
       <c r="AF79" s="4"/>
     </row>
-    <row r="80" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" s="16" customFormat="1">
       <c r="A80" s="13" t="s">
         <v>404</v>
       </c>
@@ -13054,7 +13104,7 @@
       <c r="AE80" s="13"/>
       <c r="AF80" s="13"/>
     </row>
-    <row r="81" spans="1:32" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" s="16" customFormat="1" ht="28.7">
       <c r="A81" s="13" t="s">
         <v>404</v>
       </c>
@@ -13134,7 +13184,7 @@
       <c r="AE81" s="13"/>
       <c r="AF81" s="13"/>
     </row>
-    <row r="82" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" s="16" customFormat="1">
       <c r="A82" s="13" t="s">
         <v>404</v>
       </c>
@@ -13202,7 +13252,7 @@
       <c r="AE82" s="13"/>
       <c r="AF82" s="13"/>
     </row>
-    <row r="83" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" s="16" customFormat="1">
       <c r="A83" s="13" t="s">
         <v>404</v>
       </c>
@@ -13270,7 +13320,7 @@
       <c r="AE83" s="13"/>
       <c r="AF83" s="13"/>
     </row>
-    <row r="84" spans="1:32" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" s="16" customFormat="1" ht="28.7">
       <c r="A84" s="13" t="s">
         <v>404</v>
       </c>
@@ -13348,7 +13398,7 @@
       <c r="AE84" s="13"/>
       <c r="AF84" s="13"/>
     </row>
-    <row r="85" spans="1:32" s="16" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" s="16" customFormat="1" ht="28.7">
       <c r="A85" s="13" t="s">
         <v>404</v>
       </c>
@@ -13428,7 +13478,7 @@
       <c r="AE85" s="13"/>
       <c r="AF85" s="13"/>
     </row>
-    <row r="86" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="25">
       <c r="A86" s="4" t="s">
         <v>404</v>
       </c>
@@ -13510,7 +13560,7 @@
       <c r="AE86" s="4"/>
       <c r="AF86" s="4"/>
     </row>
-    <row r="87" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="25">
       <c r="A87" s="4" t="s">
         <v>58</v>
       </c>
@@ -13590,7 +13640,7 @@
       <c r="AE87" s="4"/>
       <c r="AF87" s="4"/>
     </row>
-    <row r="88" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" s="16" customFormat="1">
       <c r="A88" s="13" t="s">
         <v>404</v>
       </c>
@@ -13664,7 +13714,7 @@
       <c r="AE88" s="13"/>
       <c r="AF88" s="13"/>
     </row>
-    <row r="89" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" s="16" customFormat="1">
       <c r="A89" s="13" t="s">
         <v>404</v>
       </c>
@@ -13738,7 +13788,7 @@
       <c r="AE89" s="13"/>
       <c r="AF89" s="13"/>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32">
       <c r="A90" s="4" t="s">
         <v>58</v>
       </c>
@@ -13820,7 +13870,7 @@
       </c>
       <c r="AF90" s="4"/>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32">
       <c r="A91" s="4" t="s">
         <v>58</v>
       </c>
@@ -13900,7 +13950,7 @@
       <c r="AE91" s="4"/>
       <c r="AF91" s="4"/>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32">
       <c r="A92" s="4" t="s">
         <v>58</v>
       </c>
@@ -13980,7 +14030,7 @@
       </c>
       <c r="AF92" s="4"/>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32">
       <c r="A93" s="4" t="s">
         <v>58</v>
       </c>
@@ -14050,7 +14100,7 @@
       <c r="AE93" s="4"/>
       <c r="AF93" s="4"/>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32">
       <c r="A94" s="4" t="s">
         <v>58</v>
       </c>
@@ -14132,7 +14182,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32">
       <c r="A95" s="4" t="s">
         <v>58</v>
       </c>
@@ -14214,7 +14264,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32">
       <c r="A96" s="4" t="s">
         <v>58</v>
       </c>
@@ -14288,7 +14338,7 @@
       <c r="AE96" s="4"/>
       <c r="AF96" s="4"/>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32">
       <c r="A97" s="4" t="s">
         <v>58</v>
       </c>
@@ -14370,7 +14420,7 @@
       </c>
       <c r="AF97" s="4"/>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32">
       <c r="A98" s="4" t="s">
         <v>58</v>
       </c>
@@ -14450,7 +14500,7 @@
       <c r="AE98" s="4"/>
       <c r="AF98" s="4"/>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32">
       <c r="A99" s="4" t="s">
         <v>58</v>
       </c>
@@ -14530,7 +14580,7 @@
       </c>
       <c r="AF99" s="4"/>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32">
       <c r="A100" s="4" t="s">
         <v>58</v>
       </c>
@@ -14600,7 +14650,7 @@
       <c r="AE100" s="4"/>
       <c r="AF100" s="4"/>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32">
       <c r="A101" s="4" t="s">
         <v>58</v>
       </c>
@@ -14682,7 +14732,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32">
       <c r="A102" s="4" t="s">
         <v>58</v>
       </c>
@@ -14764,7 +14814,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32">
       <c r="A103" s="4" t="s">
         <v>58</v>
       </c>
@@ -14838,7 +14888,7 @@
       <c r="AE103" s="4"/>
       <c r="AF103" s="4"/>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32">
       <c r="A104" s="4" t="s">
         <v>58</v>
       </c>
@@ -14920,7 +14970,7 @@
       </c>
       <c r="AF104" s="4"/>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32">
       <c r="A105" s="4" t="s">
         <v>58</v>
       </c>
@@ -15000,7 +15050,7 @@
       <c r="AE105" s="4"/>
       <c r="AF105" s="4"/>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32">
       <c r="A106" s="4" t="s">
         <v>58</v>
       </c>
@@ -15080,7 +15130,7 @@
       </c>
       <c r="AF106" s="4"/>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32">
       <c r="A107" s="4" t="s">
         <v>58</v>
       </c>
@@ -15150,7 +15200,7 @@
       <c r="AE107" s="4"/>
       <c r="AF107" s="4"/>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32">
       <c r="A108" s="4" t="s">
         <v>58</v>
       </c>
@@ -15232,7 +15282,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32">
       <c r="A109" s="4" t="s">
         <v>58</v>
       </c>
@@ -15314,7 +15364,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32">
       <c r="A110" s="4" t="s">
         <v>58</v>
       </c>
@@ -15388,7 +15438,7 @@
       <c r="AE110" s="4"/>
       <c r="AF110" s="4"/>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32">
       <c r="A111" s="4" t="s">
         <v>58</v>
       </c>
@@ -15470,7 +15520,7 @@
       </c>
       <c r="AF111" s="4"/>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32">
       <c r="A112" s="4" t="s">
         <v>58</v>
       </c>
@@ -15550,7 +15600,7 @@
       <c r="AE112" s="4"/>
       <c r="AF112" s="4"/>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:32">
       <c r="A113" s="4" t="s">
         <v>58</v>
       </c>
@@ -15630,7 +15680,7 @@
       </c>
       <c r="AF113" s="4"/>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:32">
       <c r="A114" s="4" t="s">
         <v>58</v>
       </c>
@@ -15700,7 +15750,7 @@
       <c r="AE114" s="4"/>
       <c r="AF114" s="4"/>
     </row>
-    <row r="115" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:32" ht="14.1" customHeight="1">
       <c r="A115" s="4" t="s">
         <v>58</v>
       </c>
@@ -15782,7 +15832,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="116" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:32" ht="14.1" customHeight="1">
       <c r="A116" s="4" t="s">
         <v>58</v>
       </c>
@@ -15864,7 +15914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="117" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:32" ht="14.1" customHeight="1">
       <c r="A117" s="4" t="s">
         <v>58</v>
       </c>
@@ -15938,7 +15988,7 @@
       <c r="AE117" s="4"/>
       <c r="AF117" s="4"/>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:32">
       <c r="A118" s="4" t="s">
         <v>58</v>
       </c>
@@ -16020,7 +16070,7 @@
       </c>
       <c r="AF118" s="4"/>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:32">
       <c r="A119" s="4" t="s">
         <v>58</v>
       </c>
@@ -16100,7 +16150,7 @@
       <c r="AE119" s="4"/>
       <c r="AF119" s="4"/>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:32">
       <c r="A120" s="4" t="s">
         <v>58</v>
       </c>
@@ -16180,7 +16230,7 @@
       </c>
       <c r="AF120" s="4"/>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:32">
       <c r="A121" s="4" t="s">
         <v>58</v>
       </c>
@@ -16250,7 +16300,7 @@
       <c r="AE121" s="4"/>
       <c r="AF121" s="4"/>
     </row>
-    <row r="122" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:32" ht="14.1" customHeight="1">
       <c r="A122" s="4" t="s">
         <v>58</v>
       </c>
@@ -16332,7 +16382,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:32" ht="14.1" customHeight="1">
       <c r="A123" s="4" t="s">
         <v>58</v>
       </c>
@@ -16414,7 +16464,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:32" ht="14.1" customHeight="1">
       <c r="A124" s="4" t="s">
         <v>58</v>
       </c>
@@ -16488,7 +16538,7 @@
       <c r="AE124" s="4"/>
       <c r="AF124" s="4"/>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:32">
       <c r="A125" s="4" t="s">
         <v>58</v>
       </c>
@@ -16568,7 +16618,7 @@
       </c>
       <c r="AF125" s="4"/>
     </row>
-    <row r="126" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:32" ht="25">
       <c r="A126" s="4" t="s">
         <v>58</v>
       </c>
@@ -16646,7 +16696,7 @@
       <c r="AE126" s="4"/>
       <c r="AF126" s="4"/>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:32">
       <c r="A127" s="4" t="s">
         <v>58</v>
       </c>
@@ -16730,7 +16780,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:32">
       <c r="A128" s="4" t="s">
         <v>58</v>
       </c>
@@ -16814,7 +16864,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="129" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:32" ht="25">
       <c r="A129" s="4" t="s">
         <v>58</v>
       </c>
@@ -16896,7 +16946,7 @@
       </c>
       <c r="AF129" s="4"/>
     </row>
-    <row r="130" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:32" ht="25">
       <c r="A130" s="4" t="s">
         <v>58</v>
       </c>
@@ -16976,7 +17026,7 @@
       </c>
       <c r="AF130" s="4"/>
     </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:32">
       <c r="A131" s="4" t="s">
         <v>58</v>
       </c>
@@ -17048,7 +17098,7 @@
       <c r="AE131" s="4"/>
       <c r="AF131" s="4"/>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:32">
       <c r="A132" s="4" t="s">
         <v>58</v>
       </c>
@@ -17128,7 +17178,7 @@
       </c>
       <c r="AF132" s="4"/>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:32">
       <c r="A133" s="4" t="s">
         <v>58</v>
       </c>
@@ -17206,7 +17256,7 @@
       <c r="AE133" s="4"/>
       <c r="AF133" s="4"/>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:32">
       <c r="A134" s="4" t="s">
         <v>58</v>
       </c>
@@ -17290,7 +17340,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:32">
       <c r="A135" s="4" t="s">
         <v>58</v>
       </c>
@@ -17374,7 +17424,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="136" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:32" ht="25">
       <c r="A136" s="4" t="s">
         <v>58</v>
       </c>
@@ -17454,7 +17504,7 @@
       </c>
       <c r="AF136" s="4"/>
     </row>
-    <row r="137" spans="1:32" ht="39" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:32" ht="37">
       <c r="A137" s="4" t="s">
         <v>58</v>
       </c>
@@ -17534,7 +17584,7 @@
       </c>
       <c r="AF137" s="4"/>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:32">
       <c r="A138" s="4" t="s">
         <v>58</v>
       </c>
@@ -23458,6 +23508,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Description0 xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data.</Description0>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA3DD6FD0640724CAC6A104AA4040E53" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="866aaee467307fab2f51bbdbaaea79d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dc215b4-4765-4137-95ef-e24fb8216673" xmlns:ns3="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636a025d234e12dfc0e20f1263040641" ns2:_="" ns3:_="">
     <xsd:import namespace="3dc215b4-4765-4137-95ef-e24fb8216673"/>
@@ -23714,18 +23776,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Description0 xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data.</Description0>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62FA68FA-8C71-4E93-80BA-49A20AA62094}">
   <ds:schemaRefs>
@@ -23735,6 +23785,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72C26AEA-38B4-45B2-94FF-5972E3017E52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
+    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39409D45-3830-4E57-BD4D-A5503E0F1185}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23751,15 +23812,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72C26AEA-38B4-45B2-94FF-5972E3017E52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
-    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>